--- a/Data/FlightPlan/FPL_05SEP26.xlsx
+++ b/Data/FlightPlan/FPL_05SEP26.xlsx
@@ -689,6 +689,9 @@
     <t>07:45</t>
   </si>
   <si>
+    <t>11:50</t>
+  </si>
+  <si>
     <t>HKG</t>
   </si>
   <si>
@@ -818,9 +821,6 @@
     <t>VN-A634</t>
   </si>
   <si>
-    <t>11:50</t>
-  </si>
-  <si>
     <t>21:00</t>
   </si>
   <si>
@@ -1226,7 +1226,7 @@
     <t>Total Record(s): 381</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 04, 2026 20:12</t>
+    <t xml:space="preserve">Generated on  Sep 05, 2026 00:37</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -6202,9 +6202,13 @@
       <c t="s" r="J155" s="7">
         <v>118</v>
       </c>
-      <c r="K155" s="7"/>
+      <c t="s" r="K155" s="7">
+        <v>130</v>
+      </c>
       <c r="L155" s="7"/>
-      <c r="M155" s="7"/>
+      <c t="s" r="M155" s="7">
+        <v>226</v>
+      </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
       <c t="s" r="A156" s="6">
@@ -6227,13 +6231,13 @@
         <v>80</v>
       </c>
       <c t="s" r="H156" s="8">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="I156" s="7">
         <v>209</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6257,7 +6261,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G157" s="8">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="H157" s="8">
         <v>80</v>
@@ -6299,7 +6303,7 @@
         <v>205</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6329,7 +6333,7 @@
         <v>102</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J159" s="7">
         <v>66</v>
@@ -6365,7 +6369,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6377,10 +6381,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6398,7 +6402,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6413,7 +6417,7 @@
         <v>142</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6431,7 +6435,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6446,7 +6450,7 @@
         <v>177</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6464,7 +6468,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6512,7 +6516,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6545,7 +6549,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6557,7 +6561,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="J167" s="7">
         <v>133</v>
@@ -6578,7 +6582,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6587,7 +6591,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H168" s="8">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="I168" s="7">
         <v>21</v>
@@ -6611,19 +6615,19 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G169" s="8">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="H169" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="J169" s="7">
         <v>65</v>
@@ -6659,7 +6663,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6671,7 +6675,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J171" s="7">
         <v>156</v>
@@ -6692,7 +6696,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6725,7 +6729,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6737,7 +6741,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="J173" s="7">
         <v>78</v>
@@ -6758,7 +6762,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -6773,7 +6777,7 @@
         <v>212</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -6791,7 +6795,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6824,7 +6828,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -6833,13 +6837,13 @@
         <v>68</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="I176" s="7">
         <v>98</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -6872,7 +6876,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -6881,7 +6885,7 @@
         <v>68</v>
       </c>
       <c t="s" r="H178" s="8">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="I178" s="7">
         <v>60</v>
@@ -6905,13 +6909,13 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G179" s="8">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="H179" s="8">
         <v>68</v>
@@ -6938,7 +6942,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -6953,7 +6957,7 @@
         <v>77</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -6971,7 +6975,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -6986,7 +6990,7 @@
         <v>177</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7019,7 +7023,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7052,7 +7056,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7061,13 +7065,13 @@
         <v>92</v>
       </c>
       <c t="s" r="H184" s="8">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="I184" s="7">
         <v>140</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7085,22 +7089,22 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G185" s="8">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="H185" s="8">
         <v>92</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7118,7 +7122,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7130,10 +7134,10 @@
         <v>102</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7166,7 +7170,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7181,7 +7185,7 @@
         <v>214</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7199,7 +7203,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7208,13 +7212,13 @@
         <v>68</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="I189" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7232,13 +7236,13 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="H190" s="8">
         <v>68</v>
@@ -7247,7 +7251,7 @@
         <v>50</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7265,7 +7269,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7280,7 +7284,7 @@
         <v>151</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7298,7 +7302,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7310,10 +7314,10 @@
         <v>68</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7331,7 +7335,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7346,7 +7350,7 @@
         <v>53</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7364,7 +7368,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7376,10 +7380,10 @@
         <v>68</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7412,7 +7416,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7427,7 +7431,7 @@
         <v>166</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7445,7 +7449,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7454,10 +7458,10 @@
         <v>129</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="J197" s="7">
         <v>159</v>
@@ -7478,13 +7482,13 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>68</v>
@@ -7511,7 +7515,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7523,10 +7527,10 @@
         <v>129</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7544,7 +7548,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7592,7 +7596,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7625,7 +7629,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7640,7 +7644,7 @@
         <v>66</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>269</v>
+        <v>226</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7658,7 +7662,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7691,7 +7695,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7724,7 +7728,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -7757,7 +7761,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7994,13 +7998,13 @@
         <v>68</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="I215" s="7">
         <v>106</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8024,7 +8028,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="H216" s="8">
         <v>80</v>
@@ -8060,7 +8064,7 @@
         <v>80</v>
       </c>
       <c t="s" r="H217" s="8">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="I217" s="7">
         <v>211</v>
@@ -8090,16 +8094,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G218" s="8">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="H218" s="8">
         <v>68</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8243,7 +8247,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J223" s="7">
         <v>286</v>
@@ -8312,7 +8316,7 @@
         <v>157</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8453,7 +8457,7 @@
         <v>129</v>
       </c>
       <c t="s" r="H230" s="8">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="I230" s="7">
         <v>209</v>
@@ -8483,7 +8487,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G231" s="8">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="H231" s="8">
         <v>129</v>
@@ -8519,13 +8523,13 @@
         <v>129</v>
       </c>
       <c t="s" r="H232" s="8">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="I232" s="7">
         <v>291</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8549,7 +8553,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G233" s="8">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="H233" s="8">
         <v>129</v>
@@ -8600,7 +8604,7 @@
         <v>68</v>
       </c>
       <c t="s" r="H235" s="8">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="I235" s="7">
         <v>294</v>
@@ -8630,7 +8634,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G236" s="8">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="H236" s="8">
         <v>129</v>
@@ -8639,7 +8643,7 @@
         <v>84</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -8948,10 +8952,10 @@
         <v>68</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -8993,7 +8997,7 @@
         <v>68</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="I248" s="7">
         <v>118</v>
@@ -9023,7 +9027,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="H249" s="8">
         <v>68</v>
@@ -9425,7 +9429,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9605,7 +9609,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -9701,7 +9705,7 @@
         <v>92</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J271" s="7">
         <v>301</v>
@@ -9737,7 +9741,7 @@
         <v>309</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9776,7 +9780,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G274" s="8">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="H274" s="8">
         <v>68</v>
@@ -9785,7 +9789,7 @@
         <v>155</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -9893,7 +9897,7 @@
         <v>129</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="I278" s="7">
         <v>32</v>
@@ -9923,13 +9927,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="H279" s="8">
         <v>129</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J279" s="7">
         <v>218</v>
@@ -10142,7 +10146,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J286" s="7">
         <v>125</v>
@@ -10289,7 +10293,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="J291" s="7">
         <v>23</v>
@@ -10634,7 +10638,7 @@
         <v>187</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
@@ -10664,7 +10668,7 @@
         <v>150</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="J304" s="7">
         <v>108</v>
@@ -10700,7 +10704,7 @@
         <v>325</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -11810,7 +11814,7 @@
         <v>347</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -12515,7 +12519,7 @@
         <v>119</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12548,7 +12552,7 @@
         <v>108</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -12941,7 +12945,7 @@
         <v>125</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13235,7 +13239,7 @@
         <v>375</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13514,7 +13518,7 @@
         <v>366</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -13757,7 +13761,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J407" s="7">
         <v>371</v>
@@ -13970,7 +13974,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J414" s="7">
         <v>159</v>
@@ -14120,7 +14124,7 @@
         <v>75</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -14297,7 +14301,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="J425" s="7">
         <v>198</v>
@@ -14399,7 +14403,7 @@
         <v>109</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -14429,7 +14433,7 @@
         <v>280</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="J429" s="7">
         <v>121</v>
@@ -15050,10 +15054,10 @@
         <v>129</v>
       </c>
       <c t="s" r="I450" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="J450" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
@@ -15197,7 +15201,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I455" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="J455" s="7">
         <v>33</v>
@@ -15347,7 +15351,7 @@
         <v>116</v>
       </c>
       <c t="s" r="J460" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K460" s="7"/>
       <c r="L460" s="7"/>
@@ -15430,9 +15434,13 @@
       <c t="s" r="J463" s="7">
         <v>401</v>
       </c>
-      <c r="K463" s="7"/>
+      <c t="s" r="K463" s="7">
+        <v>274</v>
+      </c>
       <c r="L463" s="7"/>
-      <c r="M463" s="7"/>
+      <c t="s" r="M463" s="7">
+        <v>107</v>
+      </c>
     </row>
     <row r="464" ht="14.25" customHeight="1">
       <c t="s" r="A464" s="6">
@@ -15463,9 +15471,13 @@
       <c t="s" r="J464" s="7">
         <v>222</v>
       </c>
-      <c r="K464" s="7"/>
+      <c t="s" r="K464" s="7">
+        <v>157</v>
+      </c>
       <c r="L464" s="7"/>
-      <c r="M464" s="7"/>
+      <c t="s" r="M464" s="7">
+        <v>21</v>
+      </c>
     </row>
     <row r="465" ht="15" customHeight="1">
       <c r="A465" s="6"/>
